--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -141,7 +141,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -163,6 +163,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -576,7 +579,7 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
           <t>•   양산품 26OP-LM83W 와 같은 납작한(저배) 구조.   코어 · 보빈 · 선재 · 권선 배치는 2–4절을 만족하는 범위에서 제작사가 정하고, 전체 높이는 첫 샘플 전에 협의한다.</t>
@@ -914,12 +917,12 @@
           <t>•</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>권선 주파수</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>130 – 292 kHz</t>
         </is>
@@ -936,12 +939,12 @@
           <t>•</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>코어 유효 단면적</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Ae  ≥  220 mm²</t>
         </is>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>B.pk ≤ 75 mT(2 T · 190 kHz)가 되는 값.   자속 경로 전체의 유효 단면: 납작한 코어는 요크가 정하고, 한 보빈에 코어 둘이면 합산.</t>
+          <t>B.pk ≤ 75 mT(2 T · 190 kHz)가 되는 값.   자속 경로 전체의 유효 단면: 납작한 코어는 요크가 정하고, 한 보빈에 코어 세트(반쪽 두 개 한 쌍) 둘을 나란히 넣으면 합산.</t>
         </is>
       </c>
     </row>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Transformer Spec" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Transformer Spec'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Transformer Spec'!$A$1:$H$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,7 +96,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -123,11 +123,44 @@
         <color rgb="00B4B4B4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -156,11 +189,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -169,6 +203,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -244,6 +281,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5334000" cy="2171700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -535,16 +602,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
     <col width="4.5" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="2.2" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="2.2" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
@@ -567,6 +635,7 @@
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
@@ -578,120 +647,106 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>•   양산품 26OP-LM83W 와 같은 납작한(저배) 구조.   코어 · 보빈 · 선재 · 권선 배치는 2–4절을 만족하는 범위에서 제작사가 정하고, 전체 높이는 첫 샘플 전에 협의한다.</t>
+          <t>•   양산품 26OP-LM83W 와 같은 납작한(저배) 구조.   코어 · 보빈은 제작사가 정하고 권선은 2절대로 한다.   전체 높이는 첫 샘플 전에 협의한다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2.    권선</t>
+          <t>2.    권선 사양</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="177" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>권선</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>단자</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>S  →  F</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>턴수</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>권선 전류           rms   /   피크</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>NP1     1차</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>1 – 2</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>5 T</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>10.9 A   /   18.2 A</t>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>선재   (구리 단면)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>위치</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>NS2     2차 A</t>
+          <t>NP1   1차</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>3 – 5</t>
+          <t>1 → 2</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>2 T</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>9.2 A   /   31.2 A</t>
+          <t>5 T</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>리츠선  ø0.10 × 370   (2.91 mm²)</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>1차 구역</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>NS3     2차 B</t>
+          <t>NS2   2차 A</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>4 – 6</t>
+          <t>3 → 5</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -699,282 +754,417 @@
           <t>2 T</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>9.2 A   /   31.2 A</t>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>리츠선  ø0.10 × 320   (2.51 mm²)</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>2차 구역, NS3 와 함께(바이파일러)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>NS3   2차 B</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>4 → 6</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>2 T</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>리츠선  ø0.10 × 320   (2.51 mm²)</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>2차 구역, NS2 와 함께(바이파일러)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>NAUX   보조</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>a – b</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NAUX  보조</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>a → b</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>1 T</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>단선  ø0.40   (0.13 mm²)</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>2차 구역, NS2 · NS3 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>감는 방향: 모든 권선을 같은 방향으로 감는다.   S = 감기 시작, F = 끝; 감기 시작(1, 3, 4, a)이 위 결선도의 점(●)이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>1차 구역과 2차 구역을 26OP-LM83W 처럼 나란히 둔다; 두 구역 사이 간격이 3절 항목 2(누설)를 정한다.   NAUX 는 전압이 2차를 따라가도록 2차 구역에 둔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>센터탭은 PCB 에서 핀 4 · 5 를 이어 만든다 — 트랜스포머 안에서 잇지 말 것.   핀마다 도체 하나; 2차 핀 하나가 권선 전류 전체(9.2 A rms)를 흘리므로 핀 전류 정격을 확인하거나 2차 끝을 바로 뽑아낼 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>구리 단면이 같거나 크고 소선이 ø0.10 이하이면 다른 선재도 된다(표피 깊이 0.14 mm, 292 kHz).   NS2 · NS3 는 두께 0.20 mm 이하 동박도 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>단자 번호는 양산품 26OP-LM83W(KH필룩스 승인원) 방식.   핀 배치는 제작사가 정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>3.    전기 요구사양</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>측정: LCR 미터, 100 kHz / 1 V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>단자</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>요구값</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="31" customHeight="1">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>인덕턴스</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>1 – 2</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>8.33 µH    ±10 %</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>다른 권선 전부 개방.   자화 + 누설 인덕턴스(자화만이 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>누설 인덕턴스</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>1 – 2</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>3.33 µH    ±10 %</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>반쪽씩: NS2 만 단락, 이어서 NS3 만 단락; 나머지 반쪽과 NAUX 는 개방.   둘 다 만족할 것.   목표값이며 최대값이 아님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>DC 중첩(포화)</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>1 – 2</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>초기 인덕턴스의 90 % 이상</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>시험 전류 17 A, 상온</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>항목 2 는 목표값이며 최대값이 아니다: 구조상 못 맞추면 샘플 전에 도달값을 알릴 것 — 2.67–3.67 µH 까지 받아들이며, 그때는 알린 값에 ±10 % 를 적용한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>NS2 · NS3 를 함께 단락하면 더 낮게 읽힌다: 기록만 하고 항목 2 의 판정에는 쓰지 말 것.   보조 권선은 단락하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>4.    동작 조건</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>권선 주파수</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>130 – 292 kHz</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>정격 부하에서 권선 전류 · 전압의 주파수; 기동 시 잠깐 527 kHz 까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>권선 전류   NP1</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>10.9 A rms   /   18.2 A 피크</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>정격 부하 — 2절의 선재로 3.74 A/mm² 이하</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>권선 전류   NS2, NS3</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>9.2 A rms   /   31.2 A 피크</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>각각, 정격 부하</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>권선 전류   NAUX</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>175 mA dc</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>센터탭은 PCB 에서 핀 4 · 5 를 이어 만든다 — 트랜스포머 안에서 잇지 말 것.   핀마다 도체 하나; 2차 핀 하나가 권선 전류 전체(9.2 A rms)를 흘리므로 핀 전류 정격을 확인하거나 2차 끝을 바로 뽑아낼 것.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>단자 번호는 양산품 26OP-LM83W(KH필룩스 승인원) 방식: 1차 1 – 2, 2차 3 – 5 · 4 – 6, 보조 a – b.   핀 배치는 제작사가 정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="38" customHeight="1">
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>도체: NP1 리츠선, 구리 단면 ≥ 2.9 mm², 소선 ≤ 0.10 mm.   NS2 · NS3 각각: 리츠선(소선 ≤ 0.10 mm) 또는 두께 ≤ 0.20 mm 동박, 구리 단면 ≥ 2.5 mm².   위 rms 전류에 3.75 A/mm² 를 적용한 값; 표피 깊이 0.17 mm(190 kHz) · 0.14 mm(292 kHz), 구리 100 °C 기준.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>NAUX: 모든 트랜스포머에 1 T.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>3.    전기 요구사양</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>측정: LCR 미터, 100 kHz / 1 V.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>단자</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>요구값</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>조건</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="31" customHeight="1">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>인덕턴스</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>1 – 2</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>8.33 µH    ±10 %</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>다른 권선 전부 개방.   자화 + 누설 인덕턴스(자화만이 아님).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>누설 인덕턴스</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>1 – 2</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>3.33 µH    ±10 %</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>반쪽씩: NS2 만 단락, 이어서 NS3 만 단락; 나머지 반쪽과 NAUX 는 개방.   둘 다 만족할 것.   목표값이며 최대값이 아님.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>DC 중첩(포화)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>1 – 2</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>초기 인덕턴스의 90 % 이상</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>시험 전류 17 A, 상온</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>항목 2 는 목표값이며 최대값이 아니다: 구조상 못 맞추면 샘플 전에 도달값을 알릴 것 — 2.67–3.67 µH 까지 받아들이며, 그때는 알린 값에 ±10 % 를 적용한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>NS2 · NS3 를 함께 단락하면 더 낮게 읽힌다: 기록만 하고 항목 2 의 판정에는 쓰지 말 것.   보조 권선은 단락하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>4.    동작 조건</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="13" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>직류 부하</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>권선 주파수</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>130 – 292 kHz</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>정격 부하에서 권선 전류 · 전압의 주파수; 기동 시 잠깐 527 kHz 까지</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="52" customHeight="1">
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>코어 유효 단면적</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>Ae  ≥  220 mm²</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>B.pk ≤ 75 mT(2 T · 190 kHz)가 되는 값.   자속 경로 전체의 유효 단면: 납작한 코어는 요크가 정하고, 한 보빈에 코어 세트(반쪽 두 개 한 쌍) 둘을 나란히 넣으면 합산.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B27:F27"/>
+  <mergeCells count="29">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B21:G21"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x3m3_KR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Transformer Spec" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Transformer Spec'!$A$1:$H$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Transformer Spec'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -174,7 +174,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,18 +191,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -602,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G37"/>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -649,10 +640,10 @@
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>•   양산품 26OP-LM83W 와 같은 납작한(저배) 구조.   코어 · 보빈은 제작사가 정하고 권선은 2절대로 한다.   전체 높이는 첫 샘플 전에 협의한다.</t>
+          <t>•   납작한(저배) 구조.   전체 높이는 첫 샘플 전에 협의.</t>
         </is>
       </c>
     </row>
@@ -724,7 +715,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>리츠선  ø0.10 × 370   (2.91 mm²)</t>
+          <t>Litz  ø0.10 × 370   (2.91 mm²)</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -756,12 +747,12 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>리츠선  ø0.10 × 320   (2.51 mm²)</t>
+          <t>Litz  ø0.10 × 320   (2.51 mm²)</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>2차 구역, NS3 와 함께(바이파일러)</t>
+          <t>2차 구역, NS3 와 함께 (bifilar)</t>
         </is>
       </c>
     </row>
@@ -788,12 +779,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>리츠선  ø0.10 × 320   (2.51 mm²)</t>
+          <t>Litz  ø0.10 × 320   (2.51 mm²)</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>2차 구역, NS2 와 함께(바이파일러)</t>
+          <t>2차 구역, NS2 와 함께 (bifilar)</t>
         </is>
       </c>
     </row>
@@ -832,336 +823,271 @@
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>감는 방향: 모든 권선을 같은 방향으로 감는다.   S = 감기 시작, F = 끝; 감기 시작(1, 3, 4, a)이 위 결선도의 점(●)이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>1차 구역과 2차 구역을 26OP-LM83W 처럼 나란히 둔다; 두 구역 사이 간격이 3절 항목 2(누설)를 정한다.   NAUX 는 전압이 2차를 따라가도록 2차 구역에 둔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>센터탭은 PCB 에서 핀 4 · 5 를 이어 만든다 — 트랜스포머 안에서 잇지 말 것.   핀마다 도체 하나; 2차 핀 하나가 권선 전류 전체(9.2 A rms)를 흘리므로 핀 전류 정격을 확인하거나 2차 끝을 바로 뽑아낼 것.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>구리 단면이 같거나 크고 소선이 ø0.10 이하이면 다른 선재도 된다(표피 깊이 0.14 mm, 292 kHz).   NS2 · NS3 는 두께 0.20 mm 이하 동박도 된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>단자 번호는 양산품 26OP-LM83W(KH필룩스 승인원) 방식.   핀 배치는 제작사가 정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+          <t>동등 선재 가능: 구리 단면 표 이상 · 소선 ≤ ø0.10 mm; NS2 · NS3 는 두께 ≤ 0.20 mm 동박도 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>3.    전기 요구사양</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="14" customHeight="1">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>측정: LCR 미터, 100 kHz / 1 V.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="7" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>단자</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>요구값</t>
         </is>
       </c>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>조건</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="31" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>인덕턴스</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>1 – 2</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>8.33 µH    ±10 %</t>
         </is>
       </c>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>다른 권선 전부 개방.   자화 + 누설 인덕턴스(자화만이 아님).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="B27" s="8" t="inlineStr">
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>다른 권선 개방</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="31" customHeight="1">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>누설 인덕턴스</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>1 – 2</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>3.33 µH    ±10 %</t>
         </is>
       </c>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>반쪽씩: NS2 만 단락, 이어서 NS3 만 단락; 나머지 반쪽과 NAUX 는 개방.   둘 다 만족할 것.   목표값이며 최대값이 아님.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>NS2 단락(NS3 · NAUX 개방); 이어서 NS3 단락(NS2 · NAUX 개방) — 둘 다</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>DC 중첩(포화)</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>1 – 2</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>초기 인덕턴스의 90 % 이상</t>
         </is>
       </c>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>시험 전류 17 A, 상온</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>항목 2 는 목표값이며 최대값이 아니다: 구조상 못 맞추면 샘플 전에 도달값을 알릴 것 — 2.67–3.67 µH 까지 받아들이며, 그때는 알린 값에 ±10 % 를 적용한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="14" customHeight="1">
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>NS2 · NS3 를 함께 단락하면 더 낮게 읽힌다: 기록만 하고 항목 2 의 판정에는 쓰지 말 것.   보조 권선은 단락하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>17 A dc, 상온</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>항목 2: 샘플 전에 알리면 2.67–3.67 µH 까지 가능, 그때 ±10 % 는 알린 값 기준.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>4.    동작 조건</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="14" t="inlineStr">
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>권선 주파수</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>130 – 292 kHz</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>정격 부하에서 권선 전류 · 전압의 주파수; 기동 시 잠깐 527 kHz 까지</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="14" t="inlineStr">
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>권선 전류   NP1</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>10.9 A rms   /   18.2 A 피크</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>정격 부하 — 2절의 선재로 3.74 A/mm² 이하</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="14" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>10.9 A rms   /   18.2 A peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>권선 전류   NS2, NS3</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>9.2 A rms   /   31.2 A 피크</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>각각, 정격 부하</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="B36" s="14" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>9.2 A rms   /   31.2 A peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>권선 전류   NAUX</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>175 mA dc</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>직류 부하</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="52" customHeight="1">
-      <c r="B37" s="14" t="inlineStr">
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>코어 유효 단면적</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>Ae  ≥  220 mm²</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>B.pk ≤ 75 mT(2 T · 190 kHz)가 되는 값.   자속 경로 전체의 유효 단면: 납작한 코어는 요크가 정하고, 한 보빈에 코어 세트(반쪽 두 개 한 쌍) 둘을 나란히 넣으면 합산.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="24">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E23:F23"/>
     <mergeCell ref="B19:G19"/>
-    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="E34:F34"/>
     <mergeCell ref="B20:G20"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B25:G25"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
